--- a/source_data/Extended_Data_Fig_2_source_data.xlsx
+++ b/source_data/Extended_Data_Fig_2_source_data.xlsx
@@ -459,7 +459,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Country averages of the assessed cities are compared with the official national reference. Agreement measures cross-scale consistency, not independent city-level validation, because national information enters GCIRI. Marker area increases with the number of assessed cities in each country.</t>
+          <t>Country averages of the assessed cities are compared with the official national reference. Because national information enters GCIRI, agreement measures cross-scale consistency. Marker area increases with the number of assessed cities in each country.</t>
         </is>
       </c>
     </row>
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75.39399999999999</v>
+        <v>75.38</v>
       </c>
       <c r="C9" t="n">
-        <v>78.23999999999999</v>
+        <v>78.05</v>
       </c>
       <c r="D9" t="n">
         <v>5</v>
@@ -822,7 +822,7 @@
         <v>2355143.903</v>
       </c>
       <c r="F9" t="n">
-        <v>78.84007825242644</v>
+        <v>78.86728288072001</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         <v>81.2</v>
       </c>
       <c r="I9" t="n">
-        <v>-5.806000000000012</v>
+        <v>-5.820000000000007</v>
       </c>
       <c r="J9" t="n">
-        <v>-5.806000000000012</v>
+        <v>-5.820000000000007</v>
       </c>
     </row>
     <row r="10">
@@ -894,7 +894,7 @@
         <v>5203452.483</v>
       </c>
       <c r="F11" t="n">
-        <v>67.96367560970347</v>
+        <v>67.96367560970346</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -918,10 +918,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>75.04166666666667</v>
+        <v>75.05743589743589</v>
       </c>
       <c r="C12" t="n">
-        <v>75.27</v>
+        <v>75.37</v>
       </c>
       <c r="D12" t="n">
         <v>78</v>
@@ -930,7 +930,7 @@
         <v>79797027.9412</v>
       </c>
       <c r="F12" t="n">
-        <v>82.33097515853891</v>
+        <v>82.33330684611987</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         <v>80.3</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.258333333333326</v>
+        <v>-5.242564102564103</v>
       </c>
       <c r="J12" t="n">
-        <v>-5.258333333333326</v>
+        <v>-5.242564102564103</v>
       </c>
     </row>
     <row r="13">
@@ -1038,7 +1038,7 @@
         <v>1446392.9127</v>
       </c>
       <c r="F15" t="n">
-        <v>31.96008908125232</v>
+        <v>31.9600890812523</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>137088904.5488</v>
       </c>
       <c r="F18" t="n">
-        <v>39.09916989609611</v>
+        <v>39.0991698960961</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>84.698125</v>
+        <v>84.720625</v>
       </c>
       <c r="C20" t="n">
         <v>85.59</v>
@@ -1218,7 +1218,7 @@
         <v>14065922.1377</v>
       </c>
       <c r="F20" t="n">
-        <v>87.46846402231823</v>
+        <v>87.47685150215595</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1229,10 +1229,10 @@
         <v>86.40000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.701875000000001</v>
+        <v>-1.679375000000007</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.701875000000001</v>
+        <v>-1.679375000000007</v>
       </c>
     </row>
     <row r="21">
@@ -1274,181 +1274,181 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IRL</t>
+          <t>ARE</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>93.55</v>
+        <v>85.02857142857144</v>
       </c>
       <c r="C22" t="n">
-        <v>93.56</v>
+        <v>84.01000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>1372382.165</v>
+        <v>6525055.7357</v>
       </c>
       <c r="F22" t="n">
-        <v>94.01564440995558</v>
+        <v>86.73323680603775</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>95.09999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.549999999999997</v>
+        <v>-1.371428571428567</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.549999999999997</v>
+        <v>-1.371428571428567</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ARE</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>84.99142857142856</v>
+        <v>82.73400000000001</v>
       </c>
       <c r="C23" t="n">
-        <v>83.8</v>
+        <v>82.34</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>6525055.7357</v>
+        <v>2894227.8038</v>
       </c>
       <c r="F23" t="n">
-        <v>86.70770239227983</v>
+        <v>82.36074780400497</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>86.40000000000001</v>
+        <v>84</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.408571428571449</v>
+        <v>-1.265999999999991</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.408571428571449</v>
+        <v>-1.265999999999991</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AUT</t>
+          <t>IRL</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>82.81399999999999</v>
+        <v>94.08333333333331</v>
       </c>
       <c r="C24" t="n">
-        <v>82.66</v>
+        <v>94.08</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>2894227.8038</v>
+        <v>1372382.165</v>
       </c>
       <c r="F24" t="n">
-        <v>82.40270265339886</v>
+        <v>94.08955463044288</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>84</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.186000000000007</v>
+        <v>-1.016666666666665</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.186000000000007</v>
+        <v>-1.01666666666668</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>KOR</t>
+          <t>SLE</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>70.28666666666666</v>
+        <v>13.866</v>
       </c>
       <c r="C25" t="n">
-        <v>70.97</v>
+        <v>16.52</v>
       </c>
       <c r="D25" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>37430822.7916</v>
+        <v>3151133.6264</v>
       </c>
       <c r="F25" t="n">
-        <v>79.47473164562322</v>
+        <v>8.058655670867616</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Republic of Korea</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>71.3</v>
+        <v>14.8</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.013333333333335</v>
+        <v>-0.9340000000000011</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.013333333333335</v>
+        <v>-0.9340000000000011</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SLE</t>
+          <t>KOR</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>13.866</v>
+        <v>70.38444444444444</v>
       </c>
       <c r="C26" t="n">
-        <v>16.52</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="E26" t="n">
-        <v>3151133.6264</v>
+        <v>37430822.7916</v>
       </c>
       <c r="F26" t="n">
-        <v>8.058655670867617</v>
+        <v>79.51126674320918</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Republic of Korea</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>14.8</v>
+        <v>71.3</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.9340000000000011</v>
+        <v>-0.9155555555555566</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.9340000000000011</v>
+        <v>-0.9155555555555566</v>
       </c>
     </row>
     <row r="27">
@@ -1490,145 +1490,145 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DZA</t>
+          <t>SVN</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>43.88607142857143</v>
+        <v>78.59</v>
       </c>
       <c r="C28" t="n">
-        <v>44.935</v>
+        <v>78.59</v>
       </c>
       <c r="D28" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>16787691.9622</v>
+        <v>252735.8561</v>
       </c>
       <c r="F28" t="n">
-        <v>43.03842467368172</v>
+        <v>78.59</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>44.5</v>
+        <v>79.3</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.6139285714285734</v>
+        <v>-0.7099999999999937</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.6139285714285734</v>
+        <v>-0.7099999999999937</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BHR</t>
+          <t>DZA</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>99.16</v>
+        <v>43.88607142857143</v>
       </c>
       <c r="C29" t="n">
-        <v>99.16</v>
+        <v>44.935</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="E29" t="n">
-        <v>1361833.134</v>
+        <v>16787691.9622</v>
       </c>
       <c r="F29" t="n">
-        <v>99.16</v>
+        <v>43.03842467368173</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>99.7</v>
+        <v>44.5</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.5400000000000063</v>
+        <v>-0.6139285714285734</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.5400000000000063</v>
+        <v>-0.6139285714285734</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>QAT</t>
+          <t>BHR</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>98.98</v>
+        <v>99.16</v>
       </c>
       <c r="C30" t="n">
-        <v>98.98</v>
+        <v>99.16</v>
       </c>
       <c r="D30" t="n">
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>1980416.128</v>
+        <v>1361833.134</v>
       </c>
       <c r="F30" t="n">
-        <v>98.98</v>
+        <v>99.16</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>99.5</v>
+        <v>99.7</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.519999999999996</v>
+        <v>-0.5400000000000063</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.519999999999996</v>
+        <v>-0.5400000000000063</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FJI</t>
+          <t>QAT</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>41.91</v>
+        <v>98.98</v>
       </c>
       <c r="C31" t="n">
-        <v>41.91</v>
+        <v>98.98</v>
       </c>
       <c r="D31" t="n">
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>242909.9953</v>
+        <v>1980416.128</v>
       </c>
       <c r="F31" t="n">
-        <v>41.91</v>
+        <v>98.98</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fiji</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>42.4</v>
+        <v>99.5</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.490000000000002</v>
+        <v>-0.519999999999996</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.490000000000002</v>
+        <v>-0.519999999999996</v>
       </c>
     </row>
     <row r="32">
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>98.5125</v>
+        <v>98.5</v>
       </c>
       <c r="C32" t="n">
         <v>98.79000000000001</v>
@@ -1650,7 +1650,7 @@
         <v>1758967.595</v>
       </c>
       <c r="F32" t="n">
-        <v>98.75641087316392</v>
+        <v>98.75162965048938</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1661,154 +1661,154 @@
         <v>99</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4874999999999971</v>
+        <v>-0.5</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.4874999999999971</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LTU</t>
+          <t>FJI</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>85.39999999999999</v>
+        <v>41.91</v>
       </c>
       <c r="C33" t="n">
-        <v>86.31999999999999</v>
+        <v>41.91</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>679540.7794</v>
+        <v>242909.9953</v>
       </c>
       <c r="F33" t="n">
-        <v>86.84281005247792</v>
+        <v>41.91</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Fiji</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>85.8</v>
+        <v>42.4</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4000000000000057</v>
+        <v>-0.490000000000002</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.4000000000000057</v>
+        <v>-0.490000000000002</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GNQ</t>
+          <t>LTU</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>32.01</v>
+        <v>85.39999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>32.01</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1519278.4729</v>
+        <v>679540.7794</v>
       </c>
       <c r="F34" t="n">
-        <v>31.9480611578703</v>
+        <v>86.84281005247792</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Equatorial Guinea</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>32.4</v>
+        <v>85.8</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3900000000000005</v>
+        <v>-0.4000000000000057</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.3900000000000005</v>
+        <v>-0.4000000000000057</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TJK</t>
+          <t>GNQ</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>29.015</v>
+        <v>32.01</v>
       </c>
       <c r="C35" t="n">
-        <v>30.435</v>
+        <v>32.01</v>
       </c>
       <c r="D35" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>2267474.81</v>
+        <v>1519278.4729</v>
       </c>
       <c r="F35" t="n">
-        <v>24.43275933050785</v>
+        <v>31.9480611578703</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tajikistan</t>
+          <t>Equatorial Guinea</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>29.4</v>
+        <v>32.4</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.384999999999998</v>
+        <v>-0.3900000000000005</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.384999999999998</v>
+        <v>-0.3900000000000005</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SVN</t>
+          <t>TJK</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>78.95999999999999</v>
+        <v>29.015</v>
       </c>
       <c r="C36" t="n">
-        <v>78.95999999999999</v>
+        <v>30.435</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>252735.8561</v>
+        <v>2267474.81</v>
       </c>
       <c r="F36" t="n">
-        <v>78.95999999999999</v>
+        <v>24.43275933050785</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Tajikistan</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>79.3</v>
+        <v>29.4</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3400000000000034</v>
+        <v>-0.384999999999998</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.3400000000000034</v>
+        <v>-0.384999999999998</v>
       </c>
     </row>
     <row r="37">
@@ -1850,73 +1850,73 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>LBY</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>89.98034482758621</v>
+        <v>79.29625</v>
       </c>
       <c r="C38" t="n">
-        <v>90.06999999999999</v>
+        <v>80.745</v>
       </c>
       <c r="D38" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="E38" t="n">
-        <v>20029189.6944</v>
+        <v>2819070.9862</v>
       </c>
       <c r="F38" t="n">
-        <v>90.49014861802866</v>
+        <v>74.92557595976545</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Libya</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>90.09999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1196551724137862</v>
+        <v>-0.1037500000000051</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.1196551724137862</v>
+        <v>-0.1037500000000051</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>LBY</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>79.29625</v>
+        <v>90.00689655172413</v>
       </c>
       <c r="C39" t="n">
-        <v>80.745</v>
+        <v>90.17</v>
       </c>
       <c r="D39" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="E39" t="n">
-        <v>2819070.9862</v>
+        <v>20029189.6944</v>
       </c>
       <c r="F39" t="n">
-        <v>74.92557595976545</v>
+        <v>90.50658379381916</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Libya</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>79.40000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1037500000000051</v>
+        <v>-0.093103448275869</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.1037500000000051</v>
+        <v>-0.093103448275869</v>
       </c>
     </row>
     <row r="40">
@@ -1962,10 +1962,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>96.47</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="C41" t="n">
-        <v>96.47</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="D41" t="n">
         <v>1</v>
@@ -1974,7 +1974,7 @@
         <v>366065.5113</v>
       </c>
       <c r="F41" t="n">
-        <v>96.47</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1985,10 +1985,10 @@
         <v>96.40000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0699999999999931</v>
+        <v>0.1400000000000005</v>
       </c>
       <c r="J41" t="n">
-        <v>0.0699999999999931</v>
+        <v>0.1400000000000005</v>
       </c>
     </row>
     <row r="42">
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>91.032</v>
+        <v>91.08</v>
       </c>
       <c r="C42" t="n">
-        <v>91.26000000000001</v>
+        <v>91.38</v>
       </c>
       <c r="D42" t="n">
         <v>5</v>
@@ -2010,7 +2010,7 @@
         <v>3082912.3969</v>
       </c>
       <c r="F42" t="n">
-        <v>91.28528819306396</v>
+        <v>91.35828078417821</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2021,154 +2021,154 @@
         <v>90.90000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>0.132000000000005</v>
+        <v>0.1799999999999926</v>
       </c>
       <c r="J42" t="n">
-        <v>0.1319999999999908</v>
+        <v>0.1799999999999926</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>EST</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>93.87</v>
+        <v>98.29571428571428</v>
       </c>
       <c r="C43" t="n">
-        <v>93.87</v>
+        <v>98.33</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E43" t="n">
-        <v>449860.9731</v>
+        <v>2960983.8422</v>
       </c>
       <c r="F43" t="n">
-        <v>93.87</v>
+        <v>98.35396212980828</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>93.59999999999999</v>
+        <v>98</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2700000000000102</v>
+        <v>0.2957142857142827</v>
       </c>
       <c r="J43" t="n">
-        <v>0.2700000000000102</v>
+        <v>0.2957142857142827</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>EST</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>98.30285714285716</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="C44" t="n">
-        <v>98.31</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2960983.8422</v>
+        <v>449860.9731</v>
       </c>
       <c r="F44" t="n">
-        <v>98.35590973689236</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>98</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3028571428571496</v>
+        <v>0.3000000000000113</v>
       </c>
       <c r="J44" t="n">
-        <v>0.3028571428571638</v>
+        <v>0.3000000000000113</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>85.1016</v>
+        <v>47.705</v>
       </c>
       <c r="C45" t="n">
-        <v>86.265</v>
+        <v>47.705</v>
       </c>
       <c r="D45" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>22557386.9637</v>
+        <v>1127654.1639</v>
       </c>
       <c r="F45" t="n">
-        <v>87.16502472893509</v>
+        <v>53.91443832362991</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Albania</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>84.59999999999999</v>
+        <v>47.1</v>
       </c>
       <c r="I45" t="n">
-        <v>0.5016000000000105</v>
+        <v>0.6049999999999969</v>
       </c>
       <c r="J45" t="n">
-        <v>0.5016000000000105</v>
+        <v>0.6049999999999969</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ALB</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>47.705</v>
+        <v>85.23379999999999</v>
       </c>
       <c r="C46" t="n">
-        <v>47.705</v>
+        <v>86.905</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E46" t="n">
-        <v>1127654.1639</v>
+        <v>22557386.9637</v>
       </c>
       <c r="F46" t="n">
-        <v>53.91443832362991</v>
+        <v>86.5060217337202</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Albania</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>47.1</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>0.6049999999999969</v>
+        <v>0.6337999999999937</v>
       </c>
       <c r="J46" t="n">
-        <v>0.6049999999999969</v>
+        <v>0.6337999999999937</v>
       </c>
     </row>
     <row r="47">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>87.9225</v>
+        <v>87.9025</v>
       </c>
       <c r="C47" t="n">
-        <v>88.24000000000001</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="D47" t="n">
         <v>4</v>
@@ -2190,7 +2190,7 @@
         <v>1811880.6798</v>
       </c>
       <c r="F47" t="n">
-        <v>88.39706905094457</v>
+        <v>88.28580099004101</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2201,10 +2201,10 @@
         <v>87</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9224999999999994</v>
+        <v>0.9025000000000034</v>
       </c>
       <c r="J47" t="n">
-        <v>0.9224999999999994</v>
+        <v>0.9025000000000034</v>
       </c>
     </row>
     <row r="48">
@@ -2214,7 +2214,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>92.50461538461538</v>
+        <v>92.5096153846154</v>
       </c>
       <c r="C48" t="n">
         <v>92.86499999999999</v>
@@ -2226,7 +2226,7 @@
         <v>24612550.9469</v>
       </c>
       <c r="F48" t="n">
-        <v>93.32991625039332</v>
+        <v>93.37201434612768</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2237,82 +2237,82 @@
         <v>91.5</v>
       </c>
       <c r="I48" t="n">
-        <v>1.004615384615377</v>
+        <v>1.009615384615387</v>
       </c>
       <c r="J48" t="n">
-        <v>1.004615384615377</v>
+        <v>1.009615384615401</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GUY</t>
+          <t>LUX</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>55.565</v>
+        <v>92.34</v>
       </c>
       <c r="C49" t="n">
-        <v>55.565</v>
+        <v>92.34</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>233832.4695</v>
+        <v>161302.506</v>
       </c>
       <c r="F49" t="n">
-        <v>54.82863673682838</v>
+        <v>92.34</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>54.3</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>1.265000000000001</v>
+        <v>1.240000000000009</v>
       </c>
       <c r="J49" t="n">
-        <v>1.265000000000001</v>
+        <v>1.240000000000009</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>LUX</t>
+          <t>GUY</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>92.43000000000001</v>
+        <v>55.565</v>
       </c>
       <c r="C50" t="n">
-        <v>92.43000000000001</v>
+        <v>55.565</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>161302.506</v>
+        <v>233832.4695</v>
       </c>
       <c r="F50" t="n">
-        <v>92.43000000000001</v>
+        <v>54.82863673682838</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>91.09999999999999</v>
+        <v>54.3</v>
       </c>
       <c r="I50" t="n">
-        <v>1.330000000000013</v>
+        <v>1.265000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>1.330000000000013</v>
+        <v>1.265000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -2406,7 +2406,7 @@
         <v>1375447.4156</v>
       </c>
       <c r="F53" t="n">
-        <v>97.03677164806111</v>
+        <v>97.03677164806112</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2426,109 +2426,109 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>88.64317073170731</v>
+        <v>93.5203896103896</v>
       </c>
       <c r="C54" t="n">
-        <v>89.44</v>
+        <v>93.84</v>
       </c>
       <c r="D54" t="n">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="E54" t="n">
-        <v>20955551.177</v>
+        <v>35412209.2379</v>
       </c>
       <c r="F54" t="n">
-        <v>86.68965805185766</v>
+        <v>93.49489651338985</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom of Great Britain and Northern Ireland</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>87.09999999999999</v>
+        <v>92</v>
       </c>
       <c r="I54" t="n">
-        <v>1.54317073170732</v>
+        <v>1.5203896103896</v>
       </c>
       <c r="J54" t="n">
-        <v>1.54317073170732</v>
+        <v>1.5203896103896</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DEU</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>91.67094339622642</v>
+        <v>88.68634146341464</v>
       </c>
       <c r="C55" t="n">
-        <v>91.81999999999999</v>
+        <v>89.28</v>
       </c>
       <c r="D55" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="E55" t="n">
-        <v>25844310.9888</v>
+        <v>20955551.177</v>
       </c>
       <c r="F55" t="n">
-        <v>91.38481726266774</v>
+        <v>86.84858574215804</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>90</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>1.67094339622642</v>
+        <v>1.586341463414641</v>
       </c>
       <c r="J55" t="n">
-        <v>1.67094339622642</v>
+        <v>1.586341463414641</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>DEU</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>93.75116883116884</v>
+        <v>91.69603773584906</v>
       </c>
       <c r="C56" t="n">
-        <v>94.37</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="D56" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="E56" t="n">
-        <v>35412209.2379</v>
+        <v>25844310.9888</v>
       </c>
       <c r="F56" t="n">
-        <v>93.95973689005361</v>
+        <v>91.40271067758673</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>United Kingdom of Great Britain and Northern Ireland</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I56" t="n">
-        <v>1.751168831168826</v>
+        <v>1.69603773584906</v>
       </c>
       <c r="J56" t="n">
-        <v>1.75116883116884</v>
+        <v>1.69603773584906</v>
       </c>
     </row>
     <row r="57">
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>87.66521739130435</v>
+        <v>87.70347826086957</v>
       </c>
       <c r="C59" t="n">
         <v>88.18000000000001</v>
@@ -2622,7 +2622,7 @@
         <v>8916151.6834</v>
       </c>
       <c r="F59" t="n">
-        <v>86.54105069187037</v>
+        <v>86.64218981908466</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2633,82 +2633,82 @@
         <v>85.8</v>
       </c>
       <c r="I59" t="n">
-        <v>1.865217391304356</v>
+        <v>1.903478260869576</v>
       </c>
       <c r="J59" t="n">
-        <v>1.865217391304356</v>
+        <v>1.903478260869576</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PRT</t>
+          <t>NLD</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>90.27833333333332</v>
+        <v>93.02636363636364</v>
       </c>
       <c r="C60" t="n">
-        <v>90.455</v>
+        <v>93.755</v>
       </c>
       <c r="D60" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="E60" t="n">
-        <v>3633996.9627</v>
+        <v>7359651.0308</v>
       </c>
       <c r="F60" t="n">
-        <v>89.98776264531631</v>
+        <v>93.3239960258686</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>88.40000000000001</v>
+        <v>91</v>
       </c>
       <c r="I60" t="n">
-        <v>1.878333333333316</v>
+        <v>2.026363636363627</v>
       </c>
       <c r="J60" t="n">
-        <v>1.878333333333316</v>
+        <v>2.026363636363641</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>NLD</t>
+          <t>PRT</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>93.00727272727272</v>
+        <v>90.47333333333334</v>
       </c>
       <c r="C61" t="n">
-        <v>93.69</v>
+        <v>90.455</v>
       </c>
       <c r="D61" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="E61" t="n">
-        <v>7359651.0308</v>
+        <v>3633996.9627</v>
       </c>
       <c r="F61" t="n">
-        <v>93.34700948460058</v>
+        <v>90.05266556633657</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>91</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>2.007272727272735</v>
+        <v>2.073333333333338</v>
       </c>
       <c r="J61" t="n">
-        <v>2.007272727272721</v>
+        <v>2.073333333333338</v>
       </c>
     </row>
     <row r="62">
@@ -2730,7 +2730,7 @@
         <v>1787928.7954</v>
       </c>
       <c r="F62" t="n">
-        <v>60.61157876802213</v>
+        <v>60.61157876802212</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>22.11</v>
+        <v>22.07777777777778</v>
       </c>
       <c r="C64" t="n">
         <v>30.26</v>
@@ -2802,7 +2802,7 @@
         <v>4671243.0252</v>
       </c>
       <c r="F64" t="n">
-        <v>10.31150964547936</v>
+        <v>10.30430663285842</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2813,10 +2813,10 @@
         <v>19.6</v>
       </c>
       <c r="I64" t="n">
-        <v>2.509999999999998</v>
+        <v>2.477777777777778</v>
       </c>
       <c r="J64" t="n">
-        <v>2.509999999999998</v>
+        <v>2.477777777777778</v>
       </c>
     </row>
     <row r="65">
@@ -2838,7 +2838,7 @@
         <v>2244160.2676</v>
       </c>
       <c r="F65" t="n">
-        <v>76.89774421644607</v>
+        <v>76.89774421644609</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>68.2642358490566</v>
+        <v>68.27858490566038</v>
       </c>
       <c r="C67" t="n">
         <v>69.61</v>
@@ -2910,7 +2910,7 @@
         <v>602473601.4828</v>
       </c>
       <c r="F67" t="n">
-        <v>71.49662561134483</v>
+        <v>71.54006273861309</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2921,154 +2921,154 @@
         <v>65.2</v>
       </c>
       <c r="I67" t="n">
-        <v>3.064235849056601</v>
+        <v>3.078584905660378</v>
       </c>
       <c r="J67" t="n">
-        <v>3.064235849056601</v>
+        <v>3.078584905660378</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>CYP</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>79.8018918918919</v>
+        <v>75.655</v>
       </c>
       <c r="C68" t="n">
-        <v>81.45</v>
+        <v>75.655</v>
       </c>
       <c r="D68" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>17641529.5394</v>
+        <v>386163.1757</v>
       </c>
       <c r="F68" t="n">
-        <v>78.0825948814765</v>
+        <v>75.63386182273153</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>76.7</v>
+        <v>72.5</v>
       </c>
       <c r="I68" t="n">
-        <v>3.101891891891896</v>
+        <v>3.155000000000001</v>
       </c>
       <c r="J68" t="n">
-        <v>3.101891891891896</v>
+        <v>3.155000000000001</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CYP</t>
+          <t>CHE</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>75.655</v>
+        <v>89.75571428571428</v>
       </c>
       <c r="C69" t="n">
-        <v>75.655</v>
+        <v>89.95</v>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E69" t="n">
-        <v>386163.1757</v>
+        <v>2139961.9762</v>
       </c>
       <c r="F69" t="n">
-        <v>75.63386182273153</v>
+        <v>90.05658777696557</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>72.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>3.155000000000001</v>
+        <v>3.155714285714282</v>
       </c>
       <c r="J69" t="n">
-        <v>3.155000000000001</v>
+        <v>3.155714285714282</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>HRV</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>76.57333333333334</v>
+        <v>79.85891891891893</v>
       </c>
       <c r="C70" t="n">
-        <v>77.03</v>
+        <v>81.45</v>
       </c>
       <c r="D70" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="E70" t="n">
-        <v>975565.9757</v>
+        <v>17641529.5394</v>
       </c>
       <c r="F70" t="n">
-        <v>77.03113326486015</v>
+        <v>78.11571988808723</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>73.40000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="I70" t="n">
-        <v>3.173333333333332</v>
+        <v>3.158918918918928</v>
       </c>
       <c r="J70" t="n">
-        <v>3.173333333333332</v>
+        <v>3.158918918918928</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CHE</t>
+          <t>HRV</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>89.78</v>
+        <v>76.57333333333334</v>
       </c>
       <c r="C71" t="n">
-        <v>90.06999999999999</v>
+        <v>77.03</v>
       </c>
       <c r="D71" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E71" t="n">
-        <v>2139961.9762</v>
+        <v>975565.9757</v>
       </c>
       <c r="F71" t="n">
-        <v>90.07517616341468</v>
+        <v>77.03113326486015</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>86.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>3.180000000000007</v>
+        <v>3.173333333333332</v>
       </c>
       <c r="J71" t="n">
-        <v>3.180000000000007</v>
+        <v>3.173333333333332</v>
       </c>
     </row>
     <row r="72">
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>83.11551351351352</v>
+        <v>83.20032432432433</v>
       </c>
       <c r="C74" t="n">
         <v>84.31999999999999</v>
@@ -3162,7 +3162,7 @@
         <v>125657692.9197</v>
       </c>
       <c r="F74" t="n">
-        <v>84.67665513547939</v>
+        <v>84.8092257712085</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3173,10 +3173,10 @@
         <v>79.59999999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>3.515513513513525</v>
+        <v>3.600324324324333</v>
       </c>
       <c r="J74" t="n">
-        <v>3.515513513513525</v>
+        <v>3.600324324324333</v>
       </c>
     </row>
     <row r="75">
@@ -3366,10 +3366,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>93.78545454545456</v>
+        <v>93.84727272727272</v>
       </c>
       <c r="C80" t="n">
-        <v>94.25</v>
+        <v>94.3</v>
       </c>
       <c r="D80" t="n">
         <v>11</v>
@@ -3378,7 +3378,7 @@
         <v>5853951.5788</v>
       </c>
       <c r="F80" t="n">
-        <v>93.48117779041682</v>
+        <v>93.58318270250516</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3389,10 +3389,10 @@
         <v>89.40000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>4.38545454545455</v>
+        <v>4.447272727272718</v>
       </c>
       <c r="J80" t="n">
-        <v>4.38545454545455</v>
+        <v>4.447272727272718</v>
       </c>
     </row>
     <row r="81">
@@ -3414,7 +3414,7 @@
         <v>26861654.9686</v>
       </c>
       <c r="F81" t="n">
-        <v>77.28102980509023</v>
+        <v>77.28102980509024</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>7893345.3664</v>
       </c>
       <c r="F88" t="n">
-        <v>82.99687241313522</v>
+        <v>82.99687241313524</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>28.16173228346457</v>
+        <v>28.15874015748032</v>
       </c>
       <c r="C90" t="n">
         <v>29.18</v>
@@ -3738,7 +3738,7 @@
         <v>82497152.3986</v>
       </c>
       <c r="F90" t="n">
-        <v>23.1310628759815</v>
+        <v>23.13028648577993</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3749,10 +3749,10 @@
         <v>22.5</v>
       </c>
       <c r="I90" t="n">
-        <v>5.661732283464566</v>
+        <v>5.658740157480313</v>
       </c>
       <c r="J90" t="n">
-        <v>5.661732283464566</v>
+        <v>5.658740157480317</v>
       </c>
     </row>
     <row r="91">
@@ -3810,7 +3810,7 @@
         <v>11890213.9902</v>
       </c>
       <c r="F92" t="n">
-        <v>56.03059073105942</v>
+        <v>56.03059073105941</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>724414.0043</v>
       </c>
       <c r="F95" t="n">
-        <v>44.4196307423153</v>
+        <v>44.41963074231529</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -4014,10 +4014,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>72.07166666666666</v>
+        <v>72.0744696969697</v>
       </c>
       <c r="C98" t="n">
-        <v>73.535</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="D98" t="n">
         <v>132</v>
@@ -4026,7 +4026,7 @@
         <v>59578214.3066</v>
       </c>
       <c r="F98" t="n">
-        <v>73.97646860892173</v>
+        <v>74.00676856460419</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -4037,10 +4037,10 @@
         <v>64.59999999999999</v>
       </c>
       <c r="I98" t="n">
-        <v>7.471666666666664</v>
+        <v>7.474469696969706</v>
       </c>
       <c r="J98" t="n">
-        <v>7.471666666666664</v>
+        <v>7.474469696969706</v>
       </c>
     </row>
     <row r="99">
@@ -4062,7 +4062,7 @@
         <v>3251736.8349</v>
       </c>
       <c r="F99" t="n">
-        <v>12.01337057445896</v>
+        <v>12.01337057445897</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>8076755.4035</v>
       </c>
       <c r="F101" t="n">
-        <v>53.31712958331696</v>
+        <v>53.31712958331697</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>29745734.6022</v>
       </c>
       <c r="F108" t="n">
-        <v>57.62863375095299</v>
+        <v>57.62863375095298</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>3685597.932</v>
       </c>
       <c r="F109" t="n">
-        <v>26.82836933689679</v>
+        <v>26.82836933689678</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>511017403.2932</v>
       </c>
       <c r="F110" t="n">
-        <v>40.31393387802954</v>
+        <v>40.31393387802955</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>82.21000000000001</v>
+        <v>82.30500000000001</v>
       </c>
       <c r="C112" t="n">
-        <v>82.21000000000001</v>
+        <v>82.30500000000001</v>
       </c>
       <c r="D112" t="n">
         <v>2</v>
@@ -4530,7 +4530,7 @@
         <v>533377.2915000001</v>
       </c>
       <c r="F112" t="n">
-        <v>82.29811117315816</v>
+        <v>82.40861221288046</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -4541,10 +4541,10 @@
         <v>72.90000000000001</v>
       </c>
       <c r="I112" t="n">
-        <v>9.310000000000002</v>
+        <v>9.404999999999999</v>
       </c>
       <c r="J112" t="n">
-        <v>9.310000000000002</v>
+        <v>9.404999999999999</v>
       </c>
     </row>
     <row r="113">
@@ -4626,7 +4626,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>28.94660714285714</v>
+        <v>28.94702380952381</v>
       </c>
       <c r="C115" t="n">
         <v>30.14</v>
@@ -4638,7 +4638,7 @@
         <v>103418713.1305</v>
       </c>
       <c r="F115" t="n">
-        <v>26.94458133890902</v>
+        <v>26.94468364265334</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -4649,10 +4649,10 @@
         <v>19</v>
       </c>
       <c r="I115" t="n">
-        <v>9.94660714285714</v>
+        <v>9.947023809523811</v>
       </c>
       <c r="J115" t="n">
-        <v>9.94660714285714</v>
+        <v>9.947023809523811</v>
       </c>
     </row>
     <row r="116">
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>50.21073684210527</v>
+        <v>50.21063157894737</v>
       </c>
       <c r="C120" t="n">
         <v>52.41</v>
@@ -4818,7 +4818,7 @@
         <v>46706256.9581</v>
       </c>
       <c r="F120" t="n">
-        <v>49.39194836916874</v>
+        <v>49.39192171031202</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -4829,10 +4829,10 @@
         <v>39.9</v>
       </c>
       <c r="I120" t="n">
-        <v>10.31073684210527</v>
+        <v>10.31063157894737</v>
       </c>
       <c r="J120" t="n">
-        <v>10.31073684210527</v>
+        <v>10.31063157894737</v>
       </c>
     </row>
     <row r="121">
@@ -4890,7 +4890,7 @@
         <v>101411079.5739</v>
       </c>
       <c r="F122" t="n">
-        <v>26.71142214144161</v>
+        <v>26.71142214144162</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>15614480.6769</v>
       </c>
       <c r="F123" t="n">
-        <v>38.50499579612107</v>
+        <v>38.50499579612106</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>2302670.2289</v>
       </c>
       <c r="F128" t="n">
-        <v>35.54337256993099</v>
+        <v>35.543372569931</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>11626644.1724</v>
       </c>
       <c r="F131" t="n">
-        <v>10.0863461899924</v>
+        <v>10.08634618999239</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>65526049.3929</v>
       </c>
       <c r="F135" t="n">
-        <v>56.09138887538652</v>
+        <v>56.09138887538653</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>4567266.059</v>
       </c>
       <c r="F139" t="n">
-        <v>36.23173861409111</v>
+        <v>36.2317386140911</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>18104490.5515</v>
       </c>
       <c r="F140" t="n">
-        <v>46.07514676966414</v>
+        <v>46.07514676966413</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>47364980.091</v>
       </c>
       <c r="F141" t="n">
-        <v>42.33943096158382</v>
+        <v>42.33943096158383</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>49788200.2018</v>
       </c>
       <c r="F143" t="n">
-        <v>62.39822390708426</v>
+        <v>62.39822390708427</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>21623457.8657</v>
       </c>
       <c r="F144" t="n">
-        <v>33.34310610439473</v>
+        <v>33.34310610439474</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>27.18659090909091</v>
+        <v>27.18545454545455</v>
       </c>
       <c r="C147" t="n">
         <v>32.17</v>
@@ -5790,7 +5790,7 @@
         <v>18948401.2968</v>
       </c>
       <c r="F147" t="n">
-        <v>18.09011746997876</v>
+        <v>18.08870103999903</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -5801,10 +5801,10 @@
         <v>8.9</v>
       </c>
       <c r="I147" t="n">
-        <v>18.28659090909091</v>
+        <v>18.28545454545455</v>
       </c>
       <c r="J147" t="n">
-        <v>18.28659090909091</v>
+        <v>18.28545454545455</v>
       </c>
     </row>
     <row r="148">
@@ -5862,7 +5862,7 @@
         <v>13011406.4337</v>
       </c>
       <c r="F149" t="n">
-        <v>34.61033793283259</v>
+        <v>34.61033793283258</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>7678035.7462</v>
       </c>
       <c r="F151" t="n">
-        <v>38.76277657936858</v>
+        <v>38.76277657936856</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>23421778.237</v>
       </c>
       <c r="F154" t="n">
-        <v>44.93569569561145</v>
+        <v>44.93569569561146</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
